--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/3531-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/3531-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6889F12B-B586-40C8-8C39-AEDA486B6F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DE98574-2061-4776-900B-2A85A44DE9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{282DC0CC-7C81-4F82-ACF9-935F06017276}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{A46FD3AF-C2B9-46FC-B02B-7EFE67C5BB29}"/>
   </bookViews>
   <sheets>
     <sheet name="3531-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1261,21 +1261,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E279F22B-E051-4BFC-A45D-924104006514}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E34CDA9-D791-41C8-96A1-82F0D6B4E558}">
   <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="9" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.21875" customWidth="1"/>
-    <col min="11" max="13" width="11.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.77734375" customWidth="1"/>
+    <col min="1" max="3" width="8.54296875" customWidth="1"/>
+    <col min="4" max="6" width="9.08984375" customWidth="1"/>
+    <col min="7" max="9" width="8.54296875" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" customWidth="1"/>
+    <col min="11" max="13" width="8.54296875" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="9.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="16"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1357,7 +1357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="17"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1394,7 +1394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2025</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2024</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2023</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2022</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2021</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2020</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2018</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2017</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2016</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2015</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2014</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2013</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2012</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2011</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2010</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2009</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="10">
         <v>2008</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2007</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="10">
         <v>2006</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2005</v>
       </c>
